--- a/logs/most_important_angle/most_important_angle_analysis.xlsx
+++ b/logs/most_important_angle/most_important_angle_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/most_important_angle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="11_1D1953ACD35056443F5B2211595ED87656CA0C19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48D44F94-8756-4EC1-B1F1-099B6109CA70}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="11_1D1953ACD35056443F5B2211595ED87656CA0C19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7283E4A-8F33-42C7-88AB-2AB86D11182B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2604" yWindow="3804" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -809,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -817,6 +817,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -951,7 +955,9 @@
       <sharedItems longText="1"/>
     </cacheField>
     <cacheField name="head_number" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="2" count="1">
+        <n v="2"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="encoding" numFmtId="0">
       <sharedItems/>
@@ -1173,7 +1179,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1252,7 +1258,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1331,7 +1337,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1410,7 +1416,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1489,7 +1495,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1568,7 +1574,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1647,7 +1653,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1726,7 +1732,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1805,7 +1811,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1884,7 +1890,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -1963,7 +1969,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2042,7 +2048,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2121,7 +2127,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2200,7 +2206,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2279,7 +2285,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2358,7 +2364,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2437,7 +2443,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2516,7 +2522,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2595,7 +2601,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2674,7 +2680,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, -1, 0, 2, -1, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2753,7 +2759,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2832,7 +2838,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2911,7 +2917,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -2990,7 +2996,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3069,7 +3075,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3148,7 +3154,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3227,7 +3233,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3306,7 +3312,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3385,7 +3391,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3464,7 +3470,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 2, 0, -1, 2, 1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3543,7 +3549,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3622,7 +3628,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3701,7 +3707,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3780,7 +3786,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3859,7 +3865,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -3938,7 +3944,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4017,7 +4023,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4096,7 +4102,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4175,7 +4181,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4254,7 +4260,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [2, 0, -1, 2, 1, -1]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4333,7 +4339,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4412,7 +4418,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4491,7 +4497,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4570,7 +4576,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4649,7 +4655,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4728,7 +4734,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4807,7 +4813,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4886,7 +4892,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -4965,7 +4971,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5044,7 +5050,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, -1, 2, 1, -1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5123,7 +5129,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5202,7 +5208,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5281,7 +5287,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5360,7 +5366,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5439,7 +5445,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5518,7 +5524,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5597,7 +5603,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5676,7 +5682,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5755,7 +5761,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5834,7 +5840,7 @@
     <b v="0"/>
     <s v="multihead"/>
     <s v="[{'features': ['sv', 'wv', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}, {'features': ['yr', 'ya', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [-1, 0, 2, -1, 1, 2]}]"/>
-    <n v="2"/>
+    <x v="0"/>
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
@@ -5899,8 +5905,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D6F89D1A-1F93-476C-9F91-19E0A03DFDF1}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:L8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D6F89D1A-1F93-476C-9F91-19E0A03DFDF1}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:L9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="77">
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -5933,7 +5939,12 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -6004,27 +6015,31 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="2">
+  <rowFields count="3">
+    <field x="17"/>
     <field x="22"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="8">
     <i>
       <x/>
     </i>
-    <i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
       <x v="1"/>
     </i>
-    <i>
+    <i r="1">
       <x v="2"/>
     </i>
-    <i>
+    <i r="1">
       <x v="3"/>
     </i>
-    <i>
+    <i r="1">
       <x v="4"/>
     </i>
-    <i>
+    <i r="1">
       <x v="5"/>
     </i>
     <i t="grand">
@@ -6095,7 +6110,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57D5EA3A-E22D-44DF-B91B-65C655382195}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57D5EA3A-E22D-44DF-B91B-65C655382195}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:D5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="77">
     <pivotField showAll="0"/>
@@ -20797,21 +20812,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BAD70A-BD00-467A-9297-5711D29BC70B}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -20853,268 +20868,306 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2">
-        <v>0.74235773032315966</v>
-      </c>
-      <c r="C2">
-        <v>-0.27034447550631091</v>
-      </c>
-      <c r="D2">
-        <v>0.81494937187722072</v>
-      </c>
-      <c r="E2">
-        <v>0.62483668654098767</v>
-      </c>
-      <c r="F2">
-        <v>0.83785952475937031</v>
-      </c>
-      <c r="G2">
-        <v>0.69178533811505638</v>
-      </c>
-      <c r="H2">
-        <v>6.9084118742846366E-3</v>
-      </c>
-      <c r="I2">
-        <v>0.26366136608588808</v>
-      </c>
-      <c r="J2">
-        <v>-0.70013749974756767</v>
-      </c>
-      <c r="K2">
-        <v>-0.65181018023785975</v>
-      </c>
-      <c r="L2">
-        <v>10</v>
+      <c r="A2" s="3">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0.49488369589088194</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.12380984609490522</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.45932600597373013</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.46936942549436583</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.63362864236136296</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.41721070973406482</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.26429811933163688</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.33944640009902638</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.18329180467970063</v>
+      </c>
+      <c r="K2" s="4">
+        <v>-0.29179693973074988</v>
+      </c>
+      <c r="L2" s="4">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3">
-        <v>0.7554947202327964</v>
-      </c>
-      <c r="C3">
-        <v>7.4726022646395135E-2</v>
-      </c>
-      <c r="D3">
-        <v>0.72786529865645522</v>
-      </c>
-      <c r="E3">
-        <v>0.68288900521553075</v>
-      </c>
-      <c r="F3">
-        <v>0.8339127236086904</v>
-      </c>
-      <c r="G3">
-        <v>0.77731185345050668</v>
-      </c>
-      <c r="H3">
-        <v>0.48944277834410937</v>
-      </c>
-      <c r="I3">
-        <v>0.37304276680204046</v>
-      </c>
-      <c r="J3">
-        <v>-0.23550973134106376</v>
-      </c>
-      <c r="K3">
-        <v>-0.3280717232195175</v>
-      </c>
-      <c r="L3">
+      <c r="A3" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.74235773032315966</v>
+      </c>
+      <c r="C3" s="4">
+        <v>-0.27034447550631091</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.81494937187722072</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.62483668654098767</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.83785952475937031</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.69178533811505638</v>
+      </c>
+      <c r="H3" s="4">
+        <v>6.9084118742846366E-3</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.26366136608588808</v>
+      </c>
+      <c r="J3" s="4">
+        <v>-0.70013749974756767</v>
+      </c>
+      <c r="K3" s="4">
+        <v>-0.65181018023785975</v>
+      </c>
+      <c r="L3" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B4">
-        <v>5.6089753597806866E-2</v>
-      </c>
-      <c r="C4">
-        <v>4.2992878580178744E-2</v>
-      </c>
-      <c r="D4">
-        <v>-8.1991745204695723E-2</v>
-      </c>
-      <c r="E4">
-        <v>2.9723671071883773E-2</v>
-      </c>
-      <c r="F4">
-        <v>0.26851504534765458</v>
-      </c>
-      <c r="G4">
-        <v>8.1120431763802708E-3</v>
-      </c>
-      <c r="H4">
-        <v>-9.3345834904157793E-2</v>
-      </c>
-      <c r="I4">
-        <v>5.8565537335057483E-2</v>
-      </c>
-      <c r="J4">
-        <v>0.28937288618384838</v>
-      </c>
-      <c r="K4">
-        <v>-8.2621074294040711E-2</v>
-      </c>
-      <c r="L4">
+      <c r="A4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.7554947202327964</v>
+      </c>
+      <c r="C4" s="4">
+        <v>7.4726022646395135E-2</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.72786529865645522</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.68288900521553075</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.8339127236086904</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.77731185345050668</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.48944277834410937</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.37304276680204046</v>
+      </c>
+      <c r="J4" s="4">
+        <v>-0.23550973134106376</v>
+      </c>
+      <c r="K4" s="4">
+        <v>-0.3280717232195175</v>
+      </c>
+      <c r="L4" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5">
-        <v>5.6162320898373717E-2</v>
-      </c>
-      <c r="C5">
-        <v>4.2403138218049738E-2</v>
-      </c>
-      <c r="D5">
-        <v>-8.2018123790073158E-2</v>
-      </c>
-      <c r="E5">
-        <v>2.9790353107624713E-2</v>
-      </c>
-      <c r="F5">
-        <v>0.26889483181052498</v>
-      </c>
-      <c r="G5">
-        <v>7.9822224654095102E-3</v>
-      </c>
-      <c r="H5">
-        <v>-9.2670533419645679E-2</v>
-      </c>
-      <c r="I5">
-        <v>5.8801872846189741E-2</v>
-      </c>
-      <c r="J5">
-        <v>0.28850657820543429</v>
-      </c>
-      <c r="K5">
-        <v>-8.5025364759784519E-2</v>
-      </c>
-      <c r="L5">
+      <c r="A5" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="4">
+        <v>5.6089753597806866E-2</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4.2992878580178744E-2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>-8.1991745204695723E-2</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2.9723671071883773E-2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.26851504534765458</v>
+      </c>
+      <c r="G5" s="4">
+        <v>8.1120431763802708E-3</v>
+      </c>
+      <c r="H5" s="4">
+        <v>-9.3345834904157793E-2</v>
+      </c>
+      <c r="I5" s="4">
+        <v>5.8565537335057483E-2</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.28937288618384838</v>
+      </c>
+      <c r="K5" s="4">
+        <v>-8.2621074294040711E-2</v>
+      </c>
+      <c r="L5" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6">
-        <v>0.68777082634225095</v>
-      </c>
-      <c r="C6">
-        <v>0.4506022194758274</v>
-      </c>
-      <c r="D6">
-        <v>0.71390852782950132</v>
-      </c>
-      <c r="E6">
-        <v>0.68932467025075073</v>
-      </c>
-      <c r="F6">
-        <v>0.81696150540184398</v>
-      </c>
-      <c r="G6">
-        <v>0.53088860188690423</v>
-      </c>
-      <c r="H6">
-        <v>0.60977901362965004</v>
-      </c>
-      <c r="I6">
-        <v>0.62293782246604623</v>
-      </c>
-      <c r="J6">
-        <v>0.76833554407143134</v>
-      </c>
-      <c r="K6">
-        <v>-0.1986435022638201</v>
-      </c>
-      <c r="L6">
+      <c r="A6" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5.6162320898373717E-2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>4.2403138218049738E-2</v>
+      </c>
+      <c r="D6" s="4">
+        <v>-8.2018123790073158E-2</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2.9790353107624713E-2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.26889483181052498</v>
+      </c>
+      <c r="G6" s="4">
+        <v>7.9822224654095102E-3</v>
+      </c>
+      <c r="H6" s="4">
+        <v>-9.2670533419645679E-2</v>
+      </c>
+      <c r="I6" s="4">
+        <v>5.8801872846189741E-2</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.28850657820543429</v>
+      </c>
+      <c r="K6" s="4">
+        <v>-8.5025364759784519E-2</v>
+      </c>
+      <c r="L6" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7">
-        <v>0.67142682395090458</v>
-      </c>
-      <c r="C7">
-        <v>0.40247929315529091</v>
-      </c>
-      <c r="D7">
-        <v>0.66324270647397299</v>
-      </c>
-      <c r="E7">
-        <v>0.7596521667794186</v>
-      </c>
-      <c r="F7">
-        <v>0.77562822324009451</v>
-      </c>
-      <c r="G7">
-        <v>0.48718419931013096</v>
-      </c>
-      <c r="H7">
-        <v>0.66567488046558054</v>
-      </c>
-      <c r="I7">
-        <v>0.65966903505893648</v>
-      </c>
-      <c r="J7">
-        <v>0.68918305070612085</v>
-      </c>
-      <c r="K7">
-        <v>-0.40460979360947713</v>
-      </c>
-      <c r="L7">
+      <c r="A7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.68777082634225095</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.4506022194758274</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.71390852782950132</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.68932467025075073</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.81696150540184398</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.53088860188690423</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.60977901362965004</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.62293782246604623</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.76833554407143134</v>
+      </c>
+      <c r="K7" s="4">
+        <v>-0.1986435022638201</v>
+      </c>
+      <c r="L7" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.67142682395090458</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.40247929315529091</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.66324270647397299</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.7596521667794186</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.77562822324009451</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.48718419931013096</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.66567488046558054</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.65966903505893648</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.68918305070612085</v>
+      </c>
+      <c r="K8" s="4">
+        <v>-0.40460979360947713</v>
+      </c>
+      <c r="L8" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="4">
         <v>0.49488369589088194</v>
       </c>
-      <c r="C8">
+      <c r="C9" s="4">
         <v>0.12380984609490522</v>
       </c>
-      <c r="D8">
+      <c r="D9" s="4">
         <v>0.45932600597373013</v>
       </c>
-      <c r="E8">
+      <c r="E9" s="4">
         <v>0.46936942549436583</v>
       </c>
-      <c r="F8">
+      <c r="F9" s="4">
         <v>0.63362864236136296</v>
       </c>
-      <c r="G8">
+      <c r="G9" s="4">
         <v>0.41721070973406482</v>
       </c>
-      <c r="H8">
+      <c r="H9" s="4">
         <v>0.26429811933163688</v>
       </c>
-      <c r="I8">
+      <c r="I9" s="4">
         <v>0.33944640009902638</v>
       </c>
-      <c r="J8">
+      <c r="J9" s="4">
         <v>0.18329180467970063</v>
       </c>
-      <c r="K8">
+      <c r="K9" s="4">
         <v>-0.29179693973074988</v>
       </c>
-      <c r="L8">
+      <c r="L9" s="4">
         <v>60</v>
       </c>
     </row>

--- a/logs/most_important_angle/most_important_angle_analysis.xlsx
+++ b/logs/most_important_angle/most_important_angle_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/most_important_angle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="11_1D1953ACD35056443F5B2211595ED87656CA0C19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7283E4A-8F33-42C7-88AB-2AB86D11182B}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_1D1953ACD35056443F5B2211595ED87656CA0C19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{043AB39C-6400-4E87-82DA-15205AC9A13C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="33" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -809,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -818,7 +818,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -5905,7 +5904,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D6F89D1A-1F93-476C-9F91-19E0A03DFDF1}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D6F89D1A-1F93-476C-9F91-19E0A03DFDF1}" name="TablaDinámica1" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:L9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="77">
     <pivotField showAll="0"/>
@@ -6097,6 +6096,28 @@
     <dataField name="Promedio de Yaw Angle Global closed R2" fld="75" subtotal="average" baseField="22" baseItem="5"/>
     <dataField name="Cuenta de model_id" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="10" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -6110,7 +6131,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57D5EA3A-E22D-44DF-B91B-65C655382195}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57D5EA3A-E22D-44DF-B91B-65C655382195}" name="TablaDinámica2" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:D5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="77">
     <pivotField showAll="0"/>
@@ -7169,7 +7190,7 @@
         <v>7.8772846397098008E-3</v>
       </c>
       <c r="BY2" t="str">
-        <f t="shared" ref="BY2:BY33" si="0">CHOOSE(MATCH("-1", _xlfn.TAKE(_xlfn.TEXTSPLIT(SUBSTITUTE(SUBSTITUTE(W2,"[",""),"]",""), ", "), 3), 0), "theta", "phi", "lambda")</f>
+        <f>CHOOSE(MATCH("-1", _xlfn.TAKE(_xlfn.TEXTSPLIT(SUBSTITUTE(SUBSTITUTE(W2,"[",""),"]",""), ", "), 3), 0), "theta", "phi", "lambda")</f>
         <v>lambda</v>
       </c>
     </row>
@@ -7400,7 +7421,7 @@
         <v>-0.27902817845106642</v>
       </c>
       <c r="BY3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="BY2:BY33" si="0">CHOOSE(MATCH("-1", _xlfn.TAKE(_xlfn.TEXTSPLIT(SUBSTITUTE(SUBSTITUTE(W3,"[",""),"]",""), ", "), 3), 0), "theta", "phi", "lambda")</f>
         <v>lambda</v>
       </c>
     </row>
@@ -20871,265 +20892,265 @@
       <c r="A2" s="3">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>0.49488369589088194</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2">
         <v>0.12380984609490522</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2">
         <v>0.45932600597373013</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2">
         <v>0.46936942549436583</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2">
         <v>0.63362864236136296</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2">
         <v>0.41721070973406482</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2">
         <v>0.26429811933163688</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2">
         <v>0.33944640009902638</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2">
         <v>0.18329180467970063</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2">
         <v>-0.29179693973074988</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>0.74235773032315966</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3">
         <v>-0.27034447550631091</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3">
         <v>0.81494937187722072</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3">
         <v>0.62483668654098767</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3">
         <v>0.83785952475937031</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3">
         <v>0.69178533811505638</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3">
         <v>6.9084118742846366E-3</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3">
         <v>0.26366136608588808</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3">
         <v>-0.70013749974756767</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3">
         <v>-0.65181018023785975</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>0.7554947202327964</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>7.4726022646395135E-2</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4">
         <v>0.72786529865645522</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4">
         <v>0.68288900521553075</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4">
         <v>0.8339127236086904</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4">
         <v>0.77731185345050668</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>0.48944277834410937</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4">
         <v>0.37304276680204046</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4">
         <v>-0.23550973134106376</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4">
         <v>-0.3280717232195175</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>5.6089753597806866E-2</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>4.2992878580178744E-2</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>-8.1991745204695723E-2</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5">
         <v>2.9723671071883773E-2</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5">
         <v>0.26851504534765458</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5">
         <v>8.1120431763802708E-3</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>-9.3345834904157793E-2</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5">
         <v>5.8565537335057483E-2</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5">
         <v>0.28937288618384838</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5">
         <v>-8.2621074294040711E-2</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>5.6162320898373717E-2</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>4.2403138218049738E-2</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6">
         <v>-8.2018123790073158E-2</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6">
         <v>2.9790353107624713E-2</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6">
         <v>0.26889483181052498</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6">
         <v>7.9822224654095102E-3</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>-9.2670533419645679E-2</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6">
         <v>5.8801872846189741E-2</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6">
         <v>0.28850657820543429</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6">
         <v>-8.5025364759784519E-2</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>0.68777082634225095</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>0.4506022194758274</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7">
         <v>0.71390852782950132</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7">
         <v>0.68932467025075073</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7">
         <v>0.81696150540184398</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7">
         <v>0.53088860188690423</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7">
         <v>0.60977901362965004</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7">
         <v>0.62293782246604623</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7">
         <v>0.76833554407143134</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7">
         <v>-0.1986435022638201</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>0.67142682395090458</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <v>0.40247929315529091</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8">
         <v>0.66324270647397299</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8">
         <v>0.7596521667794186</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8">
         <v>0.77562822324009451</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8">
         <v>0.48718419931013096</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8">
         <v>0.66567488046558054</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8">
         <v>0.65966903505893648</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8">
         <v>0.68918305070612085</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8">
         <v>-0.40460979360947713</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8">
         <v>10</v>
       </c>
     </row>
@@ -21137,41 +21158,53 @@
       <c r="A9" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>0.49488369589088194</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9">
         <v>0.12380984609490522</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9">
         <v>0.45932600597373013</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9">
         <v>0.46936942549436583</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9">
         <v>0.63362864236136296</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9">
         <v>0.41721070973406482</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9">
         <v>0.26429811933163688</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9">
         <v>0.33944640009902638</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9">
         <v>0.18329180467970063</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9">
         <v>-0.29179693973074988</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9">
         <v>60</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting pivot="1" sqref="B2:K9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.75"/>
+        <cfvo type="num" val="0.85"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
